--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484353_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484353_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3424</v>
+        <v>4.2025</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6106</v>
+        <v>3.3073</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7318</v>
+        <v>0.8952</v>
       </c>
       <c r="G2" t="n">
         <v>3.3035</v>
@@ -610,13 +610,13 @@
         <v>1.1721</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0622</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4925</v>
+        <v>0.1892</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4303</v>
+        <v>-0.2669</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5924</v>
+        <v>0.6197</v>
       </c>
       <c r="E3" t="n">
         <v>-0.1411</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7335</v>
+        <v>0.7608</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0294</v>
@@ -688,13 +688,13 @@
         <v>0.3907</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4331</v>
+        <v>-0.4058</v>
       </c>
       <c r="T3" t="n">
         <v>-0.1816</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2515</v>
+        <v>-0.2242</v>
       </c>
       <c r="V3" t="n">
         <v>0.6642</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>C. VILLALON CAYETANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2128</v>
+        <v>0.2617</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7366</v>
+        <v>-0.0801</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.5238</v>
+        <v>0.3418</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.8753</v>
+        <v>0.0361</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1737</v>
+        <v>-0.0987</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7015</v>
+        <v>0.1348</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1114</v>
+        <v>0.0409</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3287</v>
+        <v>0.0409</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7827</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9866</v>
+        <v>-0.0049</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5024</v>
+        <v>-0.1397</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4842</v>
+        <v>0.1348</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.084</v>
+        <v>-0.1651</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1294</v>
+        <v>-0.121</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2134</v>
+        <v>-0.044</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. VILLALON CAYETANO</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2072</v>
+        <v>0.1722</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0801</v>
+        <v>2.6961</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2873</v>
+        <v>-2.5238</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0361</v>
+        <v>-1.8753</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0987</v>
+        <v>-1.1737</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1348</v>
+        <v>-0.7015</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0409</v>
+        <v>1.1114</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0409</v>
+        <v>0.3287</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.7827</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0049</v>
+        <v>-2.9866</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1397</v>
+        <v>-1.5024</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1348</v>
+        <v>-1.4842</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2196</v>
+        <v>-1.1246</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.121</v>
+        <v>0.0888</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0985</v>
+        <v>-1.2134</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3892</v>
+        <v>-0.052</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1591</v>
+        <v>1.4418</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5483</v>
+        <v>-1.4938</v>
       </c>
       <c r="G6" t="n">
         <v>1.5729</v>
@@ -922,13 +922,13 @@
         <v>2.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.3408</v>
+        <v>-2.0036</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.6203</v>
+        <v>-1.3377</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7204</v>
+        <v>-0.666</v>
       </c>
       <c r="V6" t="n">
         <v>1.5507</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>I. MARTINEZ MESEGUER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1814</v>
+        <v>-0.7785</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0368</v>
+        <v>1.289</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1446</v>
+        <v>-2.0674</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1486</v>
+        <v>0.747</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5935</v>
+        <v>-3.0566</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4449</v>
+        <v>3.8036</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0609</v>
+        <v>3.2739</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0205</v>
+        <v>-1.2049</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>4.4789</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2095</v>
+        <v>-2.5269</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.614</v>
+        <v>-1.8516</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4045</v>
+        <v>-0.6753</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>2.5395</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6422</v>
+        <v>-1.1198</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.121</v>
+        <v>-0.8129</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5211</v>
+        <v>-0.3069</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. MARTINEZ MESEGUER</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1895</v>
+        <v>-1.1542</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9052</v>
+        <v>-1.0368</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0947</v>
+        <v>-0.1174</v>
       </c>
       <c r="G8" t="n">
-        <v>0.747</v>
+        <v>-0.1486</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.0566</v>
+        <v>-0.5935</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8036</v>
+        <v>0.4449</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2739</v>
+        <v>0.0609</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2049</v>
+        <v>0.0205</v>
       </c>
       <c r="L8" t="n">
-        <v>4.4789</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5269</v>
+        <v>-0.2095</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8516</v>
+        <v>-0.614</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6753</v>
+        <v>0.4045</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5395</v>
+        <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5308</v>
+        <v>-0.6149</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1967</v>
+        <v>-0.121</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3341</v>
+        <v>-0.4939</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5913</v>
+        <v>-2.4902</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3354</v>
+        <v>-0.2343</v>
       </c>
       <c r="F9" t="n">
         <v>-2.2559</v>
@@ -1156,10 +1156,10 @@
         <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4374</v>
+        <v>-0.3363</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3026</v>
+        <v>-0.2015</v>
       </c>
       <c r="U9" t="n">
         <v>-0.1348</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7692</v>
+        <v>-3.1269</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9463</v>
+        <v>-0.522</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8228</v>
+        <v>-2.6049</v>
       </c>
       <c r="G10" t="n">
         <v>-1.453</v>
@@ -1234,13 +1234,13 @@
         <v>3.1255</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.9059</v>
+        <v>-2.2637</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4525</v>
+        <v>-1.0282</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.4534</v>
+        <v>-1.2355</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3869</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0822</v>
+        <v>-4.0433</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8072</v>
+        <v>-3.1464</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.275</v>
+        <v>-0.8969</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9287</v>
+        <v>-3.6826</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.998</v>
+        <v>-1.4037</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9307</v>
+        <v>-2.2789</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4305</v>
+        <v>-1.2158</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0397</v>
+        <v>0.6574</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3908</v>
+        <v>-1.8733</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4982</v>
+        <v>-2.4668</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9583</v>
+        <v>-2.0611</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5399</v>
+        <v>-0.4056</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>2.7348</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6614</v>
+        <v>-2.5057</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2642</v>
+        <v>-0.9539</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9256</v>
+        <v>-1.5519</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8828</v>
+        <v>0.3869</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6372</v>
+        <v>-4.2977</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6313</v>
+        <v>-2.05</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0059</v>
+        <v>-2.2478</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.6826</v>
+        <v>-1.9287</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4037</v>
+        <v>-0.998</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2789</v>
+        <v>-0.9307</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2158</v>
+        <v>-0.4305</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6574</v>
+        <v>-0.0397</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8733</v>
+        <v>-0.3908</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.4668</v>
+        <v>-1.4982</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.0611</v>
+        <v>-0.9583</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4056</v>
+        <v>-0.5399</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7348</v>
+        <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.0996</v>
+        <v>-0.877</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4388</v>
+        <v>0.0214</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.6608</v>
+        <v>-0.8983</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3869</v>
+        <v>-1.8828</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3869</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.381</v>
+        <v>-6.2714</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.1772</v>
+        <v>-5.3595</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2038</v>
+        <v>-0.9119</v>
       </c>
       <c r="G13" t="n">
         <v>-2.2051</v>
@@ -1468,13 +1468,13 @@
         <v>3.7115</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3126</v>
+        <v>-1.203</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7647</v>
+        <v>-0.947</v>
       </c>
       <c r="U13" t="n">
-        <v>0.452</v>
+        <v>-0.2561</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4959</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.8662</v>
+        <v>-16.9581</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.7439</v>
+        <v>-3.836</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.1222</v>
+        <v>-13.122</v>
       </c>
       <c r="G14" t="n">
         <v>-7.1845</v>
@@ -1546,10 +1546,10 @@
         <v>21.4877</v>
       </c>
       <c r="S14" t="n">
-        <v>-13.6052</v>
+        <v>-12.6972</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.313100000000001</v>
+        <v>-5.405399999999999</v>
       </c>
       <c r="U14" t="n">
         <v>-7.2919</v>
@@ -1561,13 +1561,13 @@
         <v>2.882</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.8188</v>
+        <v>-5.818799999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.485</v>
+        <v>6.444</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2249</v>
+        <v>5.9773</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2602</v>
+        <v>0.4666</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1014</v>
+        <v>3.6654</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2123</v>
+        <v>3.4899</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8891</v>
+        <v>0.1755</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4194</v>
+        <v>5.5737</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3152</v>
+        <v>4.3183</v>
       </c>
       <c r="L15" t="n">
-        <v>2.1042</v>
+        <v>1.2554</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.318</v>
+        <v>-1.9083</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1028</v>
+        <v>-0.8283</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2152</v>
+        <v>-1.0799</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3441</v>
+        <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4738</v>
+        <v>1.4547</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2398</v>
+        <v>0.9514</v>
       </c>
       <c r="U15" t="n">
-        <v>1.234</v>
+        <v>0.5034</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4959</v>
+        <v>2.1052</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4959</v>
+        <v>2.3824</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.6946</v>
+        <v>5.1276</v>
       </c>
       <c r="E16" t="n">
-        <v>5.4717</v>
+        <v>4.1126</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2229</v>
+        <v>1.015</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6654</v>
+        <v>2.1014</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4899</v>
+        <v>1.2123</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1755</v>
+        <v>0.8891</v>
       </c>
       <c r="J16" t="n">
-        <v>5.5737</v>
+        <v>4.4194</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3183</v>
+        <v>2.3152</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2554</v>
+        <v>2.1042</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9083</v>
+        <v>-2.318</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8283</v>
+        <v>-1.1028</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0799</v>
+        <v>-1.2152</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7814</v>
+        <v>-0.586</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1488</v>
+        <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7054</v>
+        <v>2.1164</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4458</v>
+        <v>1.1275</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2596</v>
+        <v>0.9889</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1052</v>
+        <v>1.4959</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3824</v>
+        <v>1.4959</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.3424</v>
+        <v>4.3216</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4766</v>
+        <v>3.3754</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8659</v>
+        <v>0.9462</v>
       </c>
       <c r="G17" t="n">
         <v>1.1834</v>
@@ -1780,13 +1780,13 @@
         <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7218</v>
+        <v>1.701</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9245</v>
+        <v>0.8234</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7972</v>
+        <v>0.8776</v>
       </c>
       <c r="V17" t="n">
         <v>1.8279</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0111</v>
+        <v>3.0945</v>
       </c>
       <c r="E18" t="n">
-        <v>2.28</v>
+        <v>3.0122</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7311</v>
+        <v>0.0824</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5601</v>
+        <v>0.7084</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3832</v>
+        <v>1.4638</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.7554</v>
       </c>
       <c r="J18" t="n">
-        <v>1.105</v>
+        <v>2.0677</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9836</v>
+        <v>1.4735</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1214</v>
+        <v>0.5942</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-1.3593</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3996</v>
+        <v>-0.0097</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9445</v>
+        <v>-1.3496</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1721</v>
+        <v>1.1721</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>3.623</v>
+        <v>1.8234</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1284</v>
+        <v>0.9445</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4946</v>
+        <v>0.8789</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.8689</v>
+        <v>2.8651</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8132</v>
+        <v>2.5099</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0557</v>
+        <v>0.3552</v>
       </c>
       <c r="G19" t="n">
         <v>1.8056</v>
@@ -1936,13 +1936,13 @@
         <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1572</v>
+        <v>1.1535</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0731</v>
+        <v>0.7698</v>
       </c>
       <c r="U19" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.3837</v>
       </c>
       <c r="V19" t="n">
         <v>1.2735</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.0381</v>
+        <v>1.6323</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8999</v>
+        <v>0.4756</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1382</v>
+        <v>1.1567</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7084</v>
+        <v>0.1658</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4638</v>
+        <v>0.6777</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7554</v>
+        <v>-0.5118</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0677</v>
+        <v>0.0367</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4735</v>
+        <v>0.1433</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5942</v>
+        <v>-0.1066</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3593</v>
+        <v>0.1292</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0097</v>
+        <v>0.5344</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3496</v>
+        <v>-0.4052</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S20" t="n">
-        <v>0.767</v>
+        <v>1.0757</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1678</v>
+        <v>0.4389</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9348</v>
+        <v>0.6368</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1043</v>
+        <v>1.5347</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8291</v>
+        <v>2.2335</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7247</v>
+        <v>-0.6988</v>
       </c>
       <c r="G21" t="n">
         <v>2.2006</v>
@@ -2092,13 +2092,13 @@
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1186</v>
+        <v>1.549</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5668</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5518</v>
+        <v>0.5777</v>
       </c>
       <c r="V21" t="n">
         <v>-2.2149</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7805</v>
+        <v>1.2713</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1311</v>
+        <v>0.4599</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9116</v>
+        <v>0.8114</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1658</v>
+        <v>0.5601</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6777</v>
+        <v>1.3832</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5118</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0367</v>
+        <v>1.105</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1433</v>
+        <v>0.9836</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1066</v>
+        <v>0.1214</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1292</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5344</v>
+        <v>0.3996</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4052</v>
+        <v>-0.9445</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2239</v>
+        <v>1.8833</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1678</v>
+        <v>1.3083</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3917</v>
+        <v>0.575</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5348000000000001</v>
+        <v>1.0676</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4971</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0319</v>
+        <v>1.0591</v>
       </c>
       <c r="G23" t="n">
         <v>0.4837</v>
@@ -2248,13 +2248,13 @@
         <v>1.9534</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0511</v>
+        <v>0.5839</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5309</v>
+        <v>-0.0254</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5821</v>
+        <v>0.6093</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.056</v>
+        <v>-3.3048</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6921</v>
+        <v>-2.9954</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3639</v>
+        <v>-0.3094</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3012</v>
@@ -2326,13 +2326,13 @@
         <v>0.586</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5894</v>
+        <v>0.3405</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2504</v>
+        <v>-0.0529</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3389</v>
+        <v>0.3934</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.9377</v>
+        <v>-5.5138</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.9437</v>
+        <v>-5.4381</v>
       </c>
       <c r="F25" t="n">
-        <v>0.006</v>
+        <v>-0.0757</v>
       </c>
       <c r="G25" t="n">
         <v>-4.3888</v>
@@ -2404,13 +2404,13 @@
         <v>2.1488</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1738</v>
+        <v>0.5977</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4704</v>
+        <v>0.0352</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6443</v>
+        <v>0.5625</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9414</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>17.866</v>
+        <v>18.5401</v>
       </c>
       <c r="E26" t="n">
         <v>13.7314</v>
       </c>
       <c r="F26" t="n">
-        <v>4.1349</v>
+        <v>4.808699999999999</v>
       </c>
       <c r="G26" t="n">
         <v>7.1844</v>
@@ -2461,7 +2461,7 @@
         <v>14.7481</v>
       </c>
       <c r="L26" t="n">
-        <v>6.7509</v>
+        <v>6.750900000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-14.3145</v>
@@ -2473,7 +2473,7 @@
         <v>-10.7984</v>
       </c>
       <c r="P26" t="n">
-        <v>-5.860300000000001</v>
+        <v>-5.8603</v>
       </c>
       <c r="Q26" t="n">
         <v>-21.4874</v>
@@ -2482,13 +2482,13 @@
         <v>15.6274</v>
       </c>
       <c r="S26" t="n">
-        <v>13.605</v>
+        <v>14.2791</v>
       </c>
       <c r="T26" t="n">
-        <v>7.2919</v>
+        <v>7.292</v>
       </c>
       <c r="U26" t="n">
-        <v>6.313099999999999</v>
+        <v>6.9872</v>
       </c>
       <c r="V26" t="n">
         <v>2.936900000000001</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484353_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484353_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.7731</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0.3869</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-5.818799999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,11 +1873,16 @@
       <c r="X17" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0945</v>
+        <v>2.8651</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0122</v>
+        <v>2.5099</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0824</v>
+        <v>0.3552</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7084</v>
+        <v>1.8056</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4638</v>
+        <v>0.6465</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7554</v>
+        <v>1.1591</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0677</v>
+        <v>3.7837</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4735</v>
+        <v>1.6795</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5942</v>
+        <v>2.1042</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3593</v>
+        <v>-1.9781</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0097</v>
+        <v>-1.033</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3496</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1721</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8234</v>
+        <v>1.1535</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9445</v>
+        <v>0.7698</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8789</v>
+        <v>0.3837</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6093</v>
+        <v>1.2735</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6093</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1977,72 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.8651</v>
+        <v>1.8666</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5099</v>
+        <v>1.7842</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3552</v>
+        <v>0.0824</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8056</v>
+        <v>-0.5195</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6465</v>
+        <v>0.2359</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1591</v>
+        <v>-0.7554</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7837</v>
+        <v>0.8397</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6795</v>
+        <v>0.2456</v>
       </c>
       <c r="L19" t="n">
-        <v>2.1042</v>
+        <v>0.5942</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9781</v>
+        <v>-1.3593</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.033</v>
+        <v>-0.0097</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-1.3496</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1535</v>
+        <v>1.8234</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7698</v>
+        <v>0.9445</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3837</v>
+        <v>0.8789</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2735</v>
+        <v>-0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3869</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.7731</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,11 +2288,16 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2309,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.0676</v>
+        <v>1.2279</v>
       </c>
       <c r="E23" t="n">
-        <v>0.008500000000000001</v>
+        <v>1.2279</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0591</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4837</v>
+        <v>1.2279</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6091</v>
+        <v>1.2279</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0928</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9873</v>
+        <v>1.2279</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0844</v>
+        <v>1.2279</v>
       </c>
       <c r="L23" t="n">
-        <v>1.9029</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5036</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6935</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8101</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5839</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0254</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2264,12 +2370,17 @@
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2392,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3048</v>
+        <v>1.0676</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9954</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3094</v>
+        <v>1.0591</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3012</v>
+        <v>0.4837</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0338</v>
+        <v>-0.6091</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2675</v>
+        <v>1.0928</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0124</v>
+        <v>1.9873</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0409</v>
+        <v>0.0844</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.0533</v>
+        <v>1.9029</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2889</v>
+        <v>-1.5036</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0747</v>
+        <v>-0.6935</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2142</v>
+        <v>-0.8101</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.3441</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R24" t="n">
-        <v>0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3405</v>
+        <v>0.5839</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0529</v>
+        <v>-0.0254</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3934</v>
+        <v>0.6093</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2342,12 +2453,17 @@
       </c>
       <c r="X24" t="n">
         <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5138</v>
+        <v>-3.3048</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.4381</v>
+        <v>-2.9954</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0757</v>
+        <v>-0.3094</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.3888</v>
+        <v>-1.3012</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.4758</v>
+        <v>-0.0338</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.9129</v>
+        <v>-1.2675</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.2111</v>
+        <v>-0.0124</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.243</v>
+        <v>0.0409</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.968</v>
+        <v>-0.0533</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.1777</v>
+        <v>-1.2889</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.2328</v>
+        <v>-0.0747</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9449</v>
+        <v>-1.2142</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.7814</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q25" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R25" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5977</v>
+        <v>0.3405</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0352</v>
+        <v>-0.0529</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5625</v>
+        <v>0.3934</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,152 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
+        <v>-5.5138</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-5.4381</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.0757</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-4.3888</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.4758</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-2.9129</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.2111</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.243</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.968</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.1777</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.2328</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.9449</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.5977</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.0352</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.9414</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484353_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>18.5401</v>
       </c>
-      <c r="E26" t="n">
-        <v>13.7314</v>
-      </c>
-      <c r="F26" t="n">
-        <v>4.808699999999999</v>
-      </c>
-      <c r="G26" t="n">
-        <v>7.1844</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="E27" t="n">
+        <v>13.7313</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.8087</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7.184400000000002</v>
+      </c>
+      <c r="H27" t="n">
         <v>11.2319</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I27" t="n">
         <v>-4.0474</v>
       </c>
-      <c r="J26" t="n">
-        <v>21.4989</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="J27" t="n">
+        <v>21.4988</v>
+      </c>
+      <c r="K27" t="n">
         <v>14.7481</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L27" t="n">
         <v>6.750900000000001</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M27" t="n">
         <v>-14.3145</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N27" t="n">
         <v>-3.5161</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O27" t="n">
         <v>-10.7984</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P27" t="n">
         <v>-5.8603</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q27" t="n">
         <v>-21.4874</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>15.6274</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S27" t="n">
         <v>14.2791</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>7.292</v>
       </c>
-      <c r="U26" t="n">
-        <v>6.9872</v>
-      </c>
-      <c r="V26" t="n">
-        <v>2.936900000000001</v>
-      </c>
-      <c r="W26" t="n">
+      <c r="U27" t="n">
+        <v>6.987200000000001</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.9369</v>
+      </c>
+      <c r="W27" t="n">
         <v>6.4282</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X27" t="n">
         <v>-3.4913</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
